--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
@@ -1,40 +1,455 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+  <si>
+    <t>技能效果ID</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>主键；被 SkillConfig.SkillEffectId 引用</t>
+  </si>
+  <si>
+    <t>可选；可空；策划备注不驱动规则</t>
+  </si>
+  <si>
+    <t>SkillEffectId</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>SkillEffect_01</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SkillEffect_02</t>
+  </si>
+  <si>
+    <t>SkillEffect_03</t>
+  </si>
+  <si>
+    <t>SkillEffect_04</t>
+  </si>
+  <si>
+    <t>SkillEffect_05</t>
+  </si>
+  <si>
+    <t>SkillEffect_06</t>
+  </si>
+  <si>
+    <t>SkillEffect_07</t>
+  </si>
+  <si>
+    <t>SkillEffect_08</t>
+  </si>
+  <si>
+    <t>SkillEffect_09</t>
+  </si>
+  <si>
+    <t>SkillEffect_10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +457,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,136 +1045,124 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="42.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>技能效果ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>主键；被 SkillConfig.SkillEffectId 引用</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>可选；可空；策划备注不驱动规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SkillEffectId</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SkillEffect_01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SkillEffect_02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SkillEffect_03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SkillEffect_04</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SkillEffect_05</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SkillEffect_06</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SkillEffect_07</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SkillEffect_08</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SkillEffect_09</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SkillEffect_10</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
@@ -1,263 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
-  <si>
-    <t>技能效果ID</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>主键；被 SkillConfig.SkillEffectId 引用</t>
-  </si>
-  <si>
-    <t>可选；可空；策划备注不驱动规则</t>
-  </si>
-  <si>
-    <t>SkillEffectId</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>SkillEffect_01</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SkillEffect_02</t>
-  </si>
-  <si>
-    <t>SkillEffect_03</t>
-  </si>
-  <si>
-    <t>SkillEffect_04</t>
-  </si>
-  <si>
-    <t>SkillEffect_05</t>
-  </si>
-  <si>
-    <t>SkillEffect_06</t>
-  </si>
-  <si>
-    <t>SkillEffect_07</t>
-  </si>
-  <si>
-    <t>SkillEffect_08</t>
-  </si>
-  <si>
-    <t>SkillEffect_09</t>
-  </si>
-  <si>
-    <t>SkillEffect_10</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -557,154 +478,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -758,11 +679,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1049,120 +1033,424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="42.875" customWidth="1"/>
+    <col width="42.875" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>技能效果ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>主键；被 SkillConfig.SkillEffectId 引用</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>可选；可空；策划备注不驱动规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SkillEffectId</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SkillEffect_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SkillEffect_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SkillEffect_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SkillEffect_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SkillEffect_05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SkillEffect_06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SkillEffect_07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SkillEffect_08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SkillEffect_09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SkillEffect_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SkillEffect_01_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>格挡 Lv1：敌人普攻命中 Self 时 10% 伤害→0（仍判命中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SkillEffect_01_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>格挡 Lv2：15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SkillEffect_01_3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>格挡 Lv3：20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SkillEffect_01_4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>格挡 Lv4：25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SkillEffect_01_5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>格挡 Lv5：30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SkillEffect_02_1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>舒适 Lv1：Self 满血（自身血量=100%）时伤害 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SkillEffect_02_2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>舒适 Lv2：+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SkillEffect_02_3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>舒适 Lv3：+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SkillEffect_02_4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>舒适 Lv4：+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SkillEffect_02_5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>舒适 Lv5：+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SkillEffect_03_1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>连发 Lv1：EnemySingle、无 ExtraActivationCondition；攻击目标时连续攻击 3 次；BaseCD=50s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SkillEffect_03_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>连发 Lv2：同 3 次；BaseCD=40s</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SkillEffect_03_3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>连发 Lv3：同 3 次；BaseCD=30s</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SkillEffect_03_4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>连发 Lv4：同 3 次；BaseCD=20s</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SkillEffect_03_5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>连发 Lv5：同 3 次；BaseCD=10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SkillEffect_04_1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>先发制人 Lv1：EnemySingle；普攻攻击新目标敌人的第一次；攻击伤害 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SkillEffect_04_2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>先发制人 Lv2：同条件；+30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SkillEffect_04_3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>先发制人 Lv3：同条件；+40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SkillEffect_04_4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>先发制人 Lv4：同条件；+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SkillEffect_04_5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>先发制人 Lv5：同条件；+60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SkillEffect_05_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>坚挺 Lv1：Self、敌人的本次攻击导致Self死亡；HP 强制变为 1，无敌 1 秒；BaseCD=60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SkillEffect_05_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>坚挺 Lv2：同触发；无敌 2 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SkillEffect_05_3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>坚挺 Lv3：同触发；无敌 3 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SkillEffect_05_4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>坚挺 Lv4：同触发；无敌 4 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SkillEffect_05_5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>坚挺 Lv5：同触发；无敌 5 秒</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="42.875" customWidth="1" min="1" max="1"/>
@@ -1055,6 +1055,21 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>效果种类</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>效果参数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>触发钩子</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1067,6 +1082,21 @@
           <t>可选；可空；策划备注不驱动规则</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>登记制 PascalCase Token；空=未实现</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Key=Value|Key=Value|…</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>管线插入点枚举</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1079,6 +1109,21 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EffectKind</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EffectParams</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TriggerHook</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1341,6 +1386,21 @@
           <t>先发制人 Lv1：EnemySingle；普攻攻击新目标敌人的第一次；攻击伤害 +20%</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OutgoingMulOnNewTargetFirstHit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mul=1.2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1353,6 +1413,21 @@
           <t>先发制人 Lv2：同条件；+30%</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OutgoingMulOnNewTargetFirstHit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mul=1.3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1365,6 +1440,21 @@
           <t>先发制人 Lv3：同条件；+40%</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OutgoingMulOnNewTargetFirstHit</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mul=1.4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1377,6 +1467,21 @@
           <t>先发制人 Lv4：同条件；+50%</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OutgoingMulOnNewTargetFirstHit</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mul=1.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1389,6 +1494,21 @@
           <t>先发制人 Lv5：同条件；+60%</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OutgoingMulOnNewTargetFirstHit</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mul=1.6</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1401,6 +1521,21 @@
           <t>坚挺 Lv1：Self、敌人的本次攻击导致Self死亡；HP 强制变为 1，无敌 1 秒；BaseCD=60s</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CheatDeathInvincible</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>InvincibleSeconds=1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OnWarriorWouldDie</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1413,6 +1548,21 @@
           <t>坚挺 Lv2：同触发；无敌 2 秒</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CheatDeathInvincible</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>InvincibleSeconds=2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OnWarriorWouldDie</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1425,6 +1575,21 @@
           <t>坚挺 Lv3：同触发；无敌 3 秒</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CheatDeathInvincible</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>InvincibleSeconds=3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OnWarriorWouldDie</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1437,6 +1602,21 @@
           <t>坚挺 Lv4：同触发；无敌 4 秒</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CheatDeathInvincible</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>InvincibleSeconds=4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OnWarriorWouldDie</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1447,6 +1627,1013 @@
       <c r="B38" t="inlineStr">
         <is>
           <t>坚挺 Lv5：同触发；无敌 5 秒</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CheatDeathInvincible</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>InvincibleSeconds=5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OnWarriorWouldDie</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SkillEffect_06_1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>震晕 Lv1：10% AOE 击晕 1s；半径 1.5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OnAaHitChanceAoeStun</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chance=0.1|Radius=1.5|StunSeconds=1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SkillEffect_06_2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>震晕 Lv2：击晕 2s</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OnAaHitChanceAoeStun</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chance=0.1|Radius=1.5|StunSeconds=2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SkillEffect_06_3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>震晕 Lv3：击晕 3s</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OnAaHitChanceAoeStun</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chance=0.1|Radius=1.5|StunSeconds=3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SkillEffect_06_4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>震晕 Lv4：击晕 4s</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OnAaHitChanceAoeStun</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Chance=0.1|Radius=1.5|StunSeconds=4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SkillEffect_06_5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>震晕 Lv5：击晕 5s</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OnAaHitChanceAoeStun</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chance=0.1|Radius=1.5|StunSeconds=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SkillEffect_07_1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>冰冻 Lv1：AOE 减速 2s；内置 CD 10s</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OnAaHitAoeSlow</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Radius=1.5|SlowMoveMul=0.5|SlowAttackMul=0.5|DurationSeconds=2|InternalCooldownSeconds=10</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SkillEffect_07_2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>冰冻 Lv2：减速 3s</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OnAaHitAoeSlow</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Radius=1.5|SlowMoveMul=0.5|SlowAttackMul=0.5|DurationSeconds=3|InternalCooldownSeconds=10</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SkillEffect_07_3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>冰冻 Lv3：减速 4s</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OnAaHitAoeSlow</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Radius=1.5|SlowMoveMul=0.5|SlowAttackMul=0.5|DurationSeconds=4|InternalCooldownSeconds=10</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SkillEffect_07_4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>冰冻 Lv4：减速 5s</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OnAaHitAoeSlow</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Radius=1.5|SlowMoveMul=0.5|SlowAttackMul=0.5|DurationSeconds=5|InternalCooldownSeconds=10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SkillEffect_07_5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>冰冻 Lv5：减速 6s</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OnAaHitAoeSlow</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Radius=1.5|SlowMoveMul=0.5|SlowAttackMul=0.5|DurationSeconds=6|InternalCooldownSeconds=10</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SkillEffect_08_1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>精英克制 Lv1：EnemySingle Elite +50%</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OutgoingMulVsMonsterType</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MonsterType=Elite|Mul=1.5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SkillEffect_08_2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>精英克制 Lv2：Elite +60%</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OutgoingMulVsMonsterType</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MonsterType=Elite|Mul=1.6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SkillEffect_08_3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>精英克制 Lv3：Elite +70%</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OutgoingMulVsMonsterType</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MonsterType=Elite|Mul=1.7</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SkillEffect_08_4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>精英克制 Lv4：Elite +80%</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OutgoingMulVsMonsterType</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MonsterType=Elite|Mul=1.8</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SkillEffect_08_5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>精英克制 Lv5：Elite +90%</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OutgoingMulVsMonsterType</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MonsterType=Elite|Mul=1.9</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OnOutgoingDamageSettle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SkillEffect_09_1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>渐入佳境 Lv1：+3%/10s，cap 60%</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>StackingOutgoingMulTimed</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>StackBonus=0.03|MaxTotalBonus=0.6|TickSeconds=10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OnSkillInternalCooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SkillEffect_09_2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>渐入佳境 Lv2：+5%/10s，cap 60%</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>StackingOutgoingMulTimed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>StackBonus=0.05|MaxTotalBonus=0.6|TickSeconds=10</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OnSkillInternalCooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SkillEffect_09_3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>渐入佳境 Lv3：+7%/10s，cap 60%</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>StackingOutgoingMulTimed</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>StackBonus=0.07|MaxTotalBonus=0.6|TickSeconds=10</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OnSkillInternalCooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SkillEffect_09_4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>渐入佳境 Lv4：+9%/10s，cap 60%</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>StackingOutgoingMulTimed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>StackBonus=0.09|MaxTotalBonus=0.6|TickSeconds=10</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OnSkillInternalCooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SkillEffect_09_5</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>渐入佳境 Lv5：+12%/10s，cap 60%</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>StackingOutgoingMulTimed</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>StackBonus=0.12|MaxTotalBonus=0.6|TickSeconds=10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OnSkillInternalCooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SkillEffect_10_1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>贯穿 Lv1：再穿 1 名；100%</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>RangedPierceExtraHits</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ExtraHitCount=1|DamageMul=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SkillEffect_10_2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>贯穿 Lv2：再穿 2 名；100%</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RangedPierceExtraHits</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ExtraHitCount=2|DamageMul=1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SkillEffect_10_3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>贯穿 Lv3：再穿 3 名；100%</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>RangedPierceExtraHits</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ExtraHitCount=3|DamageMul=1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SkillEffect_10_4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>贯穿 Lv4：再穿 4 名；100%</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>RangedPierceExtraHits</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ExtraHitCount=4|DamageMul=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SkillEffect_10_5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>贯穿 Lv5：再穿 5 名；100%</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>RangedPierceExtraHits</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ExtraHitCount=5|DamageMul=1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SkillEffect_11_1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>灼烧 Lv1：20% NAP/1s × 2s；叠时</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OnAaHitApplyBurn</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TickDamageMul=0.2|TickIntervalSeconds=1|DurationSeconds=2|StackMode=RefreshDuration</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SkillEffect_11_2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>灼烧 Lv2：持续 3s</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OnAaHitApplyBurn</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TickDamageMul=0.2|TickIntervalSeconds=1|DurationSeconds=3|StackMode=RefreshDuration</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SkillEffect_11_3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>灼烧 Lv3：持续 4s</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OnAaHitApplyBurn</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TickDamageMul=0.2|TickIntervalSeconds=1|DurationSeconds=4|StackMode=RefreshDuration</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SkillEffect_11_4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>灼烧 Lv4：持续 5s</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OnAaHitApplyBurn</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TickDamageMul=0.2|TickIntervalSeconds=1|DurationSeconds=5|StackMode=RefreshDuration</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SkillEffect_11_5</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>灼烧 Lv5：持续 6s</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OnAaHitApplyBurn</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TickDamageMul=0.2|TickIntervalSeconds=1|DurationSeconds=6|StackMode=RefreshDuration</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OnWarriorAaHitConfirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SkillEffect_12_1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>瞬移 Lv1：最远敌背后；BaseCD=60</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RetargetFarthestTeleportBehind</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OnWarriorTargetAcquired</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SkillEffect_12_2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>瞬移 Lv2：BaseCD=50</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>RetargetFarthestTeleportBehind</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OnWarriorTargetAcquired</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SkillEffect_12_3</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>瞬移 Lv3：BaseCD=40</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RetargetFarthestTeleportBehind</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OnWarriorTargetAcquired</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SkillEffect_12_4</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>瞬移 Lv4：BaseCD=30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>RetargetFarthestTeleportBehind</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OnWarriorTargetAcquired</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SkillEffect_12_5</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>瞬移 Lv5：BaseCD=20</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>RetargetFarthestTeleportBehind</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OnWarriorTargetAcquired</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BondEffect_IronWall_1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>铜墙铁壁 I：战士 MaxHP +3%（展示；Handler 未接线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BondEffect_IronWall_2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>铜墙铁壁 II：战士 MaxHP +5%（展示；Handler 未接线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BondEffect_HumanLegion_1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>人类军团：展示用羁绊（Handler 未接线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BondEffect_FullArmy_1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>满编：展示用羁绊（Handler 未接线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BondEffect_StrStrength_1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>力之共鸣：展示用羁绊（Handler 未接线）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BondEffect_PreciseClass_1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>近卫专精：展示用羁绊（Handler 未接线）</t>
         </is>
       </c>
     </row>
